--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA2A18F-F8FA-4AB2-8044-E4ED8AFB3152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F66F72B-6946-4138-9789-98C04EADBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="238">
   <si>
     <t>country_name</t>
   </si>
@@ -527,9 +527,6 @@
     <t>categorical</t>
   </si>
   <si>
-    <t>numerical</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
@@ -542,9 +539,6 @@
     <t>ordinal</t>
   </si>
   <si>
-    <t>ratio</t>
-  </si>
-  <si>
     <t>Name of the country</t>
   </si>
   <si>
@@ -600,6 +594,165 @@
   </si>
   <si>
     <t>subnational</t>
+  </si>
+  <si>
+    <t>discrete</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>continuous</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Nat. Leader</t>
+  </si>
+  <si>
+    <t>Nat. Leader Sex</t>
+  </si>
+  <si>
+    <t>Nat. Term</t>
+  </si>
+  <si>
+    <t>Nat. Yrs in Office</t>
+  </si>
+  <si>
+    <t>Nat. Reelected</t>
+  </si>
+  <si>
+    <t>Nat. Early Exit</t>
+  </si>
+  <si>
+    <t>Nat. Party</t>
+  </si>
+  <si>
+    <t>Nat. Ideology</t>
+  </si>
+  <si>
+    <t>Nat. Election Yr</t>
+  </si>
+  <si>
+    <t>Subnat. Leader</t>
+  </si>
+  <si>
+    <t>Subnat. Leader Sex</t>
+  </si>
+  <si>
+    <t>Subnat. Term</t>
+  </si>
+  <si>
+    <t>Subnat. Leader Change</t>
+  </si>
+  <si>
+    <t>Subnat. Leader Changes</t>
+  </si>
+  <si>
+    <t>Subnat. Yrs in Office</t>
+  </si>
+  <si>
+    <t>Subnat. Early Exit</t>
+  </si>
+  <si>
+    <t>Subnat. Reelected</t>
+  </si>
+  <si>
+    <t>Subnat. Continuous Yrs</t>
+  </si>
+  <si>
+    <t>Subnat. Party</t>
+  </si>
+  <si>
+    <t>Subnat. Party Change</t>
+  </si>
+  <si>
+    <t>Subnat. Party Changes</t>
+  </si>
+  <si>
+    <t>Subnat. Party Tenure</t>
+  </si>
+  <si>
+    <t>Subnat. Ideology</t>
+  </si>
+  <si>
+    <t>Subnat. Election Yr</t>
+  </si>
+  <si>
+    <t>Subnat. Election Count</t>
+  </si>
+  <si>
+    <t>Concurrent Elections</t>
+  </si>
+  <si>
+    <t>Gov. Alignment</t>
+  </si>
+  <si>
+    <t>Extraordinary Election</t>
+  </si>
+  <si>
+    <t>Subnat. Election Date</t>
+  </si>
+  <si>
+    <t>Reg. Voters</t>
+  </si>
+  <si>
+    <t>Total Votes</t>
+  </si>
+  <si>
+    <t>Turnout Rate</t>
+  </si>
+  <si>
+    <t>Valid Votes</t>
+  </si>
+  <si>
+    <t>Invalid Votes</t>
+  </si>
+  <si>
+    <t>Winner Votes</t>
+  </si>
+  <si>
+    <t>2nd Place Votes</t>
+  </si>
+  <si>
+    <t>Last Place Votes</t>
+  </si>
+  <si>
+    <t>Victory Margin</t>
+  </si>
+  <si>
+    <t>Parties Running</t>
+  </si>
+  <si>
+    <t>Effective Parties</t>
+  </si>
+  <si>
+    <t>pretty_name</t>
+  </si>
+  <si>
+    <t>Valid Vote Ratio</t>
+  </si>
+  <si>
+    <t>Invalid Vote Ratio</t>
+  </si>
+  <si>
+    <t>Winner Ratio</t>
+  </si>
+  <si>
+    <t>2nd Place Ratio</t>
+  </si>
+  <si>
+    <t>Last Place Ratio</t>
   </si>
 </sst>
 </file>
@@ -926,1788 +1079,1846 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="85.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
         <v>182</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
         <v>169</v>
       </c>
       <c r="D4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" t="s">
         <v>161</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>161</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
-        <v>164</v>
-      </c>
       <c r="E7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="F7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
-        <v>162</v>
-      </c>
       <c r="E9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" t="s">
-        <v>164</v>
-      </c>
       <c r="E10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="s">
-        <v>164</v>
-      </c>
       <c r="E11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>161</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="C13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" t="s">
-        <v>166</v>
-      </c>
       <c r="E13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="F13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
-        <v>164</v>
-      </c>
       <c r="E14" t="s">
-        <v>176</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" t="s">
         <v>25</v>
       </c>
-      <c r="D15" t="s">
-        <v>163</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D16" t="s">
         <v>27</v>
       </c>
-      <c r="D16" t="s">
-        <v>164</v>
-      </c>
       <c r="E16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" t="s">
         <v>31</v>
       </c>
-      <c r="D18" t="s">
-        <v>164</v>
-      </c>
       <c r="E18" t="s">
-        <v>176</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="C19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="D19" t="s">
-        <v>162</v>
-      </c>
       <c r="E19" t="s">
-        <v>177</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F19" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="C20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" t="s">
         <v>35</v>
       </c>
-      <c r="D20" t="s">
-        <v>162</v>
-      </c>
       <c r="E20" t="s">
-        <v>177</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="C21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" t="s">
         <v>37</v>
       </c>
-      <c r="D21" t="s">
-        <v>164</v>
-      </c>
       <c r="E21" t="s">
-        <v>176</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F21" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" t="s">
         <v>39</v>
       </c>
-      <c r="D22" t="s">
-        <v>164</v>
-      </c>
       <c r="E22" t="s">
-        <v>176</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F22" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="C23" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" t="s">
         <v>41</v>
       </c>
-      <c r="D23" t="s">
-        <v>162</v>
-      </c>
       <c r="E23" t="s">
-        <v>177</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F23" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="C24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" t="s">
         <v>43</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>161</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="C25" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" t="s">
         <v>45</v>
       </c>
-      <c r="D25" t="s">
-        <v>164</v>
-      </c>
       <c r="E25" t="s">
-        <v>176</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="C26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" t="s">
         <v>47</v>
       </c>
-      <c r="D26" t="s">
-        <v>162</v>
-      </c>
       <c r="E26" t="s">
-        <v>177</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="C27" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" t="s">
         <v>49</v>
       </c>
-      <c r="D27" t="s">
-        <v>162</v>
-      </c>
       <c r="E27" t="s">
-        <v>177</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="C28" t="s">
+        <v>169</v>
+      </c>
+      <c r="D28" t="s">
         <v>51</v>
       </c>
-      <c r="D28" t="s">
-        <v>166</v>
-      </c>
       <c r="E28" t="s">
-        <v>179</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="F28" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="C29" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" t="s">
         <v>53</v>
       </c>
-      <c r="D29" t="s">
-        <v>164</v>
-      </c>
       <c r="E29" t="s">
-        <v>176</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F29" t="s">
+        <v>174</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="C30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" t="s">
         <v>55</v>
       </c>
-      <c r="D30" t="s">
-        <v>162</v>
-      </c>
       <c r="E30" t="s">
-        <v>177</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F30" t="s">
+        <v>175</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="C31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" t="s">
         <v>57</v>
       </c>
-      <c r="D31" t="s">
-        <v>164</v>
-      </c>
       <c r="E31" t="s">
-        <v>176</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F31" t="s">
+        <v>174</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="C32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" t="s">
         <v>59</v>
       </c>
-      <c r="D32" t="s">
-        <v>164</v>
-      </c>
       <c r="E32" t="s">
-        <v>176</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F32" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="C33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" t="s">
         <v>61</v>
       </c>
-      <c r="D33" t="s">
-        <v>164</v>
-      </c>
       <c r="E33" t="s">
-        <v>176</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" t="s">
         <v>63</v>
       </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>164</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="C35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" t="s">
         <v>65</v>
       </c>
-      <c r="D35" t="s">
-        <v>162</v>
-      </c>
       <c r="E35" t="s">
-        <v>178</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F35" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
         <v>67</v>
       </c>
-      <c r="D36" t="s">
-        <v>162</v>
-      </c>
       <c r="E36" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F36" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="C37" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" t="s">
         <v>69</v>
       </c>
-      <c r="D37" t="s">
-        <v>167</v>
-      </c>
       <c r="E37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F37" t="s">
+        <v>179</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="C38" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" t="s">
         <v>71</v>
       </c>
-      <c r="D38" t="s">
-        <v>162</v>
-      </c>
       <c r="E38" t="s">
-        <v>178</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F38" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" t="s">
         <v>73</v>
       </c>
-      <c r="D39" t="s">
-        <v>167</v>
-      </c>
       <c r="E39" t="s">
-        <v>181</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F39" t="s">
+        <v>179</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="C40" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" t="s">
         <v>75</v>
       </c>
-      <c r="D40" t="s">
-        <v>162</v>
-      </c>
       <c r="E40" t="s">
-        <v>178</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F40" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C41" t="s">
+        <v>170</v>
+      </c>
+      <c r="D41" t="s">
         <v>77</v>
       </c>
-      <c r="D41" t="s">
-        <v>167</v>
-      </c>
       <c r="E41" t="s">
-        <v>181</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F41" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="C42" t="s">
+        <v>170</v>
+      </c>
+      <c r="D42" t="s">
         <v>79</v>
       </c>
-      <c r="D42" t="s">
-        <v>162</v>
-      </c>
       <c r="E42" t="s">
-        <v>178</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" t="s">
         <v>81</v>
       </c>
-      <c r="D43" t="s">
-        <v>167</v>
-      </c>
       <c r="E43" t="s">
-        <v>181</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F43" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="C44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" t="s">
         <v>83</v>
       </c>
-      <c r="D44" t="s">
-        <v>162</v>
-      </c>
       <c r="E44" t="s">
-        <v>178</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F44" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
         <v>85</v>
       </c>
-      <c r="D45" t="s">
-        <v>167</v>
-      </c>
       <c r="E45" t="s">
-        <v>181</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" t="s">
         <v>87</v>
       </c>
-      <c r="D46" t="s">
-        <v>162</v>
-      </c>
       <c r="E46" t="s">
-        <v>178</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="C47" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" t="s">
         <v>89</v>
       </c>
-      <c r="D47" t="s">
-        <v>167</v>
-      </c>
       <c r="E47" t="s">
-        <v>181</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F47" t="s">
+        <v>179</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="C48" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" t="s">
         <v>91</v>
       </c>
-      <c r="D48" t="s">
-        <v>162</v>
-      </c>
       <c r="E48" t="s">
-        <v>178</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F48" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="C49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" t="s">
         <v>93</v>
       </c>
-      <c r="D49" t="s">
-        <v>162</v>
-      </c>
       <c r="E49" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F49" t="s">
+        <v>176</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>94</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" t="s">
         <v>95</v>
       </c>
-      <c r="D50" t="s">
-        <v>162</v>
-      </c>
       <c r="E50" t="s">
-        <v>178</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="F50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>96</v>
       </c>
-      <c r="B51" t="s">
-        <v>174</v>
-      </c>
       <c r="C51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D51" t="s">
         <v>97</v>
       </c>
-      <c r="D51" t="s">
-        <v>166</v>
-      </c>
-      <c r="E51" t="s">
-        <v>180</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F51" t="s">
+        <v>178</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>98</v>
       </c>
-      <c r="B52" t="s">
-        <v>174</v>
-      </c>
       <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
         <v>99</v>
       </c>
-      <c r="D52" t="s">
-        <v>165</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>100</v>
       </c>
-      <c r="B53" t="s">
-        <v>174</v>
-      </c>
       <c r="C53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" t="s">
         <v>101</v>
       </c>
-      <c r="D53" t="s">
-        <v>162</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>102</v>
       </c>
-      <c r="B54" t="s">
-        <v>174</v>
-      </c>
       <c r="C54" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" t="s">
         <v>103</v>
       </c>
-      <c r="D54" t="s">
-        <v>162</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
-      <c r="B55" t="s">
-        <v>174</v>
-      </c>
       <c r="C55" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" t="s">
         <v>105</v>
       </c>
-      <c r="D55" t="s">
-        <v>167</v>
-      </c>
-      <c r="E55" t="s">
-        <v>181</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F55" t="s">
+        <v>179</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>106</v>
       </c>
-      <c r="B56" t="s">
-        <v>174</v>
-      </c>
       <c r="C56" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" t="s">
         <v>107</v>
       </c>
-      <c r="D56" t="s">
-        <v>162</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
-      <c r="B57" t="s">
-        <v>174</v>
-      </c>
       <c r="C57" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" t="s">
         <v>109</v>
       </c>
-      <c r="D57" t="s">
-        <v>167</v>
-      </c>
-      <c r="E57" t="s">
-        <v>181</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F57" t="s">
+        <v>179</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
-      <c r="B58" t="s">
-        <v>174</v>
-      </c>
       <c r="C58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" t="s">
         <v>111</v>
       </c>
-      <c r="D58" t="s">
-        <v>162</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
-      <c r="B59" t="s">
-        <v>174</v>
-      </c>
       <c r="C59" t="s">
+        <v>172</v>
+      </c>
+      <c r="D59" t="s">
         <v>113</v>
       </c>
-      <c r="D59" t="s">
-        <v>167</v>
-      </c>
-      <c r="E59" t="s">
-        <v>181</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F59" t="s">
+        <v>179</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>114</v>
       </c>
-      <c r="B60" t="s">
-        <v>174</v>
-      </c>
       <c r="C60" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" t="s">
         <v>115</v>
       </c>
-      <c r="D60" t="s">
-        <v>162</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>116</v>
       </c>
-      <c r="B61" t="s">
-        <v>174</v>
-      </c>
       <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
         <v>117</v>
       </c>
-      <c r="D61" t="s">
-        <v>167</v>
-      </c>
-      <c r="E61" t="s">
-        <v>181</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F61" t="s">
+        <v>179</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
-      <c r="B62" t="s">
-        <v>174</v>
-      </c>
       <c r="C62" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" t="s">
         <v>119</v>
       </c>
-      <c r="D62" t="s">
-        <v>162</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>120</v>
       </c>
-      <c r="B63" t="s">
-        <v>174</v>
-      </c>
       <c r="C63" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" t="s">
         <v>121</v>
       </c>
-      <c r="D63" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" t="s">
-        <v>181</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F63" t="s">
+        <v>179</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>122</v>
       </c>
-      <c r="B64" t="s">
-        <v>174</v>
-      </c>
       <c r="C64" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" t="s">
         <v>123</v>
       </c>
-      <c r="D64" t="s">
-        <v>162</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>124</v>
       </c>
-      <c r="B65" t="s">
-        <v>174</v>
-      </c>
       <c r="C65" t="s">
+        <v>172</v>
+      </c>
+      <c r="D65" t="s">
         <v>125</v>
       </c>
-      <c r="D65" t="s">
-        <v>167</v>
-      </c>
-      <c r="E65" t="s">
-        <v>181</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F65" t="s">
+        <v>179</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
-      <c r="B66" t="s">
-        <v>174</v>
-      </c>
       <c r="C66" t="s">
+        <v>172</v>
+      </c>
+      <c r="D66" t="s">
         <v>127</v>
       </c>
-      <c r="D66" t="s">
-        <v>162</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" t="s">
+        <v>129</v>
+      </c>
+      <c r="F67" t="s">
         <v>174</v>
       </c>
-      <c r="C67" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" t="s">
-        <v>164</v>
-      </c>
-      <c r="E67" t="s">
-        <v>176</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>130</v>
       </c>
-      <c r="B68" t="s">
-        <v>174</v>
-      </c>
       <c r="C68" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" t="s">
         <v>131</v>
       </c>
-      <c r="D68" t="s">
-        <v>162</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>172</v>
+      </c>
+      <c r="D69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" t="s">
         <v>174</v>
       </c>
-      <c r="C69" t="s">
-        <v>133</v>
-      </c>
-      <c r="D69" t="s">
-        <v>164</v>
-      </c>
-      <c r="E69" t="s">
-        <v>176</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>134</v>
       </c>
-      <c r="B70" t="s">
-        <v>174</v>
-      </c>
       <c r="C70" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" t="s">
         <v>135</v>
       </c>
-      <c r="D70" t="s">
-        <v>162</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>136</v>
       </c>
-      <c r="B71" t="s">
-        <v>174</v>
-      </c>
       <c r="C71" t="s">
+        <v>172</v>
+      </c>
+      <c r="D71" t="s">
         <v>137</v>
       </c>
-      <c r="D71" t="s">
-        <v>162</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>138</v>
       </c>
-      <c r="B72" t="s">
-        <v>174</v>
-      </c>
       <c r="C72" t="s">
+        <v>172</v>
+      </c>
+      <c r="D72" t="s">
         <v>139</v>
       </c>
-      <c r="D72" t="s">
-        <v>162</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>140</v>
       </c>
-      <c r="B73" t="s">
-        <v>174</v>
-      </c>
       <c r="C73" t="s">
+        <v>172</v>
+      </c>
+      <c r="D73" t="s">
         <v>141</v>
       </c>
-      <c r="D73" t="s">
-        <v>167</v>
-      </c>
-      <c r="E73" t="s">
-        <v>181</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F73" t="s">
+        <v>179</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>142</v>
       </c>
-      <c r="B74" t="s">
-        <v>174</v>
-      </c>
       <c r="C74" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" t="s">
         <v>143</v>
       </c>
-      <c r="D74" t="s">
-        <v>162</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>144</v>
       </c>
-      <c r="B75" t="s">
-        <v>174</v>
-      </c>
       <c r="C75" t="s">
+        <v>172</v>
+      </c>
+      <c r="D75" t="s">
         <v>145</v>
       </c>
-      <c r="D75" t="s">
-        <v>167</v>
-      </c>
-      <c r="E75" t="s">
-        <v>181</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F75" t="s">
+        <v>179</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>146</v>
       </c>
-      <c r="B76" t="s">
-        <v>174</v>
-      </c>
       <c r="C76" t="s">
+        <v>172</v>
+      </c>
+      <c r="D76" t="s">
         <v>147</v>
       </c>
-      <c r="D76" t="s">
-        <v>162</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-      <c r="G76" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>148</v>
       </c>
-      <c r="B77" t="s">
-        <v>174</v>
-      </c>
       <c r="C77" t="s">
+        <v>172</v>
+      </c>
+      <c r="D77" t="s">
         <v>149</v>
       </c>
-      <c r="D77" t="s">
-        <v>162</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-      <c r="G77" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>150</v>
       </c>
-      <c r="B78" t="s">
-        <v>173</v>
-      </c>
       <c r="C78" t="s">
+        <v>171</v>
+      </c>
+      <c r="D78" t="s">
         <v>151</v>
       </c>
-      <c r="D78" t="s">
-        <v>162</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-      <c r="G78" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>152</v>
       </c>
-      <c r="B79" t="s">
-        <v>173</v>
-      </c>
       <c r="C79" t="s">
+        <v>171</v>
+      </c>
+      <c r="D79" t="s">
         <v>153</v>
       </c>
-      <c r="D79" t="s">
-        <v>162</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>154</v>
       </c>
-      <c r="B80" t="s">
-        <v>173</v>
-      </c>
       <c r="C80" t="s">
+        <v>171</v>
+      </c>
+      <c r="D80" t="s">
         <v>155</v>
       </c>
-      <c r="D80" t="s">
-        <v>162</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-      <c r="G80" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>156</v>
       </c>
-      <c r="B81" t="s">
-        <v>173</v>
-      </c>
       <c r="C81" t="s">
+        <v>171</v>
+      </c>
+      <c r="D81" t="s">
         <v>157</v>
       </c>
-      <c r="D81" t="s">
-        <v>162</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="G81" t="s">
-        <v>186</v>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F66F72B-6946-4138-9789-98C04EADBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1EE2D8-F125-4AB2-83E8-F3C5B054DF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="239">
   <si>
     <t>country_name</t>
   </si>
@@ -753,6 +753,9 @@
   </si>
   <si>
     <t>Last Place Ratio</t>
+  </si>
+  <si>
+    <t>#ff8000,#00E5FF</t>
   </si>
 </sst>
 </file>
@@ -1079,6 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1115,7 +1119,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1142,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1161,7 +1165,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1184,7 +1188,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1207,7 +1211,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1247,7 +1251,7 @@
         <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1256,7 +1260,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1322,7 +1326,7 @@
         <v>163</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1348,7 +1352,7 @@
         <v>163</v>
       </c>
       <c r="F11" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1357,7 +1361,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1380,7 +1384,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1423,7 +1427,7 @@
         <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1432,7 +1436,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1472,7 +1476,7 @@
         <v>186</v>
       </c>
       <c r="F16" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1481,7 +1485,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1521,7 +1525,7 @@
         <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1530,7 +1534,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1556,7 +1560,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1599,7 +1603,7 @@
         <v>163</v>
       </c>
       <c r="F21" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1625,7 +1629,7 @@
         <v>163</v>
       </c>
       <c r="F22" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1634,7 +1638,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1660,7 +1664,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1709,7 +1713,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1735,7 +1739,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -1761,7 +1765,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1804,7 +1808,7 @@
         <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1813,7 +1817,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1856,7 +1860,7 @@
         <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1882,7 +1886,7 @@
         <v>163</v>
       </c>
       <c r="F32" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1908,7 +1912,7 @@
         <v>163</v>
       </c>
       <c r="F33" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1917,7 +1921,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1940,7 +1944,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -1966,7 +1970,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -1992,7 +1996,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2018,7 +2022,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2044,7 +2048,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2070,7 +2074,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2096,7 +2100,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2122,7 +2126,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2148,7 +2152,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2174,7 +2178,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2200,7 +2204,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -2226,7 +2230,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2252,7 +2256,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -2278,7 +2282,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>90</v>
       </c>
@@ -2304,7 +2308,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>92</v>
       </c>
@@ -2330,7 +2334,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -2356,7 +2360,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -2376,7 +2380,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -2393,7 +2397,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -2410,7 +2414,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>102</v>
       </c>
@@ -2427,7 +2431,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2447,7 +2451,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>106</v>
       </c>
@@ -2464,7 +2468,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -2484,7 +2488,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2501,7 +2505,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -2521,7 +2525,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -2538,7 +2542,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>116</v>
       </c>
@@ -2558,7 +2562,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2575,7 +2579,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2595,7 +2599,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2612,7 +2616,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -2632,7 +2636,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2649,7 +2653,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -2669,7 +2673,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -2686,7 +2690,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -2706,7 +2710,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>134</v>
       </c>
@@ -2723,7 +2727,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>136</v>
       </c>
@@ -2740,7 +2744,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>138</v>
       </c>
@@ -2757,7 +2761,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -2777,7 +2781,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -2814,7 +2818,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -2831,7 +2835,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -2848,7 +2852,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>150</v>
       </c>
@@ -2865,7 +2869,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>152</v>
       </c>
@@ -2882,7 +2886,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -2899,7 +2903,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -2917,7 +2921,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="binary"/>
+        <filter val="gender"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1EE2D8-F125-4AB2-83E8-F3C5B054DF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AF2356-F7DF-4A11-8EEA-88F8BB118EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="240">
   <si>
     <t>country_name</t>
   </si>
@@ -756,13 +756,16 @@
   </si>
   <si>
     <t>#ff8000,#00E5FF</t>
+  </si>
+  <si>
+    <t>#1f77b4,#ff7f0e,#2ca02c,#d62728,#9467bd,#e377c2,#8c564b,#bcbd22,#17becf,#aec7e8,#ffbb78,#98df8a,#d95f02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,6 +775,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -799,9 +810,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1082,8 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -1091,6 +1105,7 @@
     <col min="4" max="4" width="85.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1119,7 +1134,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1157,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1165,7 +1180,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1203,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1226,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1260,7 +1275,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1283,7 +1298,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1361,7 +1376,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1384,7 +1399,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1436,7 +1451,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1485,7 +1500,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1508,7 +1523,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1534,7 +1549,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1560,7 +1575,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1586,7 +1601,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -1612,7 +1627,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1638,7 +1653,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1664,7 +1679,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1680,14 +1695,18 @@
       <c r="E24" t="s">
         <v>161</v>
       </c>
+      <c r="F24" t="s">
+        <v>239</v>
+      </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1703,7 +1722,7 @@
       <c r="E25" t="s">
         <v>163</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="3" t="s">
         <v>238</v>
       </c>
       <c r="G25">
@@ -1713,7 +1732,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1739,7 +1758,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -1765,7 +1784,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1791,7 +1810,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1817,7 +1836,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1843,7 +1862,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -1869,7 +1888,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -1921,7 +1940,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1944,7 +1963,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -1970,7 +1989,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -1996,7 +2015,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2022,7 +2041,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2048,7 +2067,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2074,7 +2093,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2100,7 +2119,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2126,7 +2145,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2152,7 +2171,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2178,7 +2197,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2204,7 +2223,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -2230,7 +2249,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2256,7 +2275,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -2282,7 +2301,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>90</v>
       </c>
@@ -2308,7 +2327,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>92</v>
       </c>
@@ -2334,7 +2353,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -2360,7 +2379,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -2380,7 +2399,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -2397,7 +2416,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -2414,7 +2433,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>102</v>
       </c>
@@ -2431,7 +2450,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2451,7 +2470,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>106</v>
       </c>
@@ -2468,7 +2487,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -2488,7 +2507,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2505,7 +2524,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -2525,7 +2544,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -2542,7 +2561,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>116</v>
       </c>
@@ -2562,7 +2581,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2579,7 +2598,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2599,7 +2618,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2616,7 +2635,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -2636,7 +2655,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2653,7 +2672,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -2673,7 +2692,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -2690,7 +2709,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -2710,7 +2729,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>134</v>
       </c>
@@ -2727,7 +2746,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>136</v>
       </c>
@@ -2744,7 +2763,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>138</v>
       </c>
@@ -2761,7 +2780,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -2781,7 +2800,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -2798,7 +2817,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -2818,7 +2837,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -2835,7 +2854,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -2852,7 +2871,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>150</v>
       </c>
@@ -2869,7 +2888,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>152</v>
       </c>
@@ -2886,7 +2905,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -2903,7 +2922,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -2921,14 +2940,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="binary"/>
-        <filter val="gender"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AF2356-F7DF-4A11-8EEA-88F8BB118EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8296709D-C474-4BEA-9C62-A2443E66E88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="241">
   <si>
     <t>country_name</t>
   </si>
@@ -759,6 +759,9 @@
   </si>
   <si>
     <t>#1f77b4,#ff7f0e,#2ca02c,#d62728,#9467bd,#e377c2,#8c564b,#bcbd22,#17becf,#aec7e8,#ffbb78,#98df8a,#d95f02</t>
+  </si>
+  <si>
+    <t>percentage</t>
   </si>
 </sst>
 </file>
@@ -1097,6 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1134,7 +1138,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +1161,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1180,7 +1184,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1203,7 +1207,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1226,7 +1230,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1249,7 +1253,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1275,7 +1279,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1298,7 +1302,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1324,7 +1328,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1350,7 +1354,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1376,7 +1380,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1399,7 +1403,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1425,7 +1429,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1451,7 +1455,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1474,7 +1478,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1500,7 +1504,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1523,7 +1527,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1549,7 +1553,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1575,7 +1579,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1601,7 +1605,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -1627,7 +1631,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1653,7 +1657,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1679,7 +1683,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1706,7 +1710,7 @@
       </c>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1732,7 +1736,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1758,7 +1762,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -1784,7 +1788,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1810,7 +1814,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1836,7 +1840,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1862,7 +1866,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -1888,7 +1892,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -1914,7 +1918,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -1940,7 +1944,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1963,7 +1967,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -1989,7 +1993,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -2029,7 +2033,7 @@
         <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F37" t="s">
         <v>179</v>
@@ -2041,7 +2045,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2081,7 +2085,7 @@
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F39" t="s">
         <v>179</v>
@@ -2093,7 +2097,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2133,7 +2137,7 @@
         <v>77</v>
       </c>
       <c r="E41" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F41" t="s">
         <v>179</v>
@@ -2145,7 +2149,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2185,7 +2189,7 @@
         <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F43" t="s">
         <v>179</v>
@@ -2197,7 +2201,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2237,7 +2241,7 @@
         <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
@@ -2249,7 +2253,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2289,7 +2293,7 @@
         <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F47" t="s">
         <v>179</v>
@@ -2315,7 +2319,7 @@
         <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="F48" t="s">
         <v>176</v>
@@ -2327,7 +2331,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>92</v>
       </c>
@@ -2379,7 +2383,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -2399,7 +2403,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -2433,7 +2437,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>102</v>
       </c>
@@ -2450,7 +2454,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2470,7 +2474,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>106</v>
       </c>
@@ -2487,7 +2491,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -2507,7 +2511,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2524,7 +2528,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -2544,7 +2548,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -2561,7 +2565,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>116</v>
       </c>
@@ -2581,7 +2585,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2598,7 +2602,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2618,7 +2622,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2635,7 +2639,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -2655,7 +2659,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2672,7 +2676,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -2692,7 +2696,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -2709,7 +2713,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -2729,7 +2733,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>134</v>
       </c>
@@ -2746,7 +2750,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>136</v>
       </c>
@@ -2763,7 +2767,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>138</v>
       </c>
@@ -2780,7 +2784,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -2800,7 +2804,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -2817,7 +2821,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -2837,7 +2841,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -2854,7 +2858,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -2871,7 +2875,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>150</v>
       </c>
@@ -2888,7 +2892,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>152</v>
       </c>
@@ -2905,7 +2909,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -2922,7 +2926,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -2940,7 +2944,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="continuous"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8296709D-C474-4BEA-9C62-A2443E66E88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC2ADD5-6D0A-40DC-B21A-CFDC2751D9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="240">
   <si>
     <t>country_name</t>
   </si>
@@ -756,9 +756,6 @@
   </si>
   <si>
     <t>#ff8000,#00E5FF</t>
-  </si>
-  <si>
-    <t>#1f77b4,#ff7f0e,#2ca02c,#d62728,#9467bd,#e377c2,#8c564b,#bcbd22,#17becf,#aec7e8,#ffbb78,#98df8a,#d95f02</t>
   </si>
   <si>
     <t>percentage</t>
@@ -1102,17 +1099,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="38.85546875" customWidth="1"/>
-    <col min="4" max="4" width="85.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="38.88671875" customWidth="1"/>
+    <col min="4" max="4" width="85.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
@@ -1138,7 +1135,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1158,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1184,7 +1181,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1207,7 +1204,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1230,7 +1227,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1253,7 +1250,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1276,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1302,7 +1299,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1325,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1354,7 +1351,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1380,7 +1377,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1403,7 +1400,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1429,7 +1426,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1455,7 +1452,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1478,7 +1475,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1504,7 +1501,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1527,7 +1524,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1553,7 +1550,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1579,7 +1576,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1605,7 +1602,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -1631,7 +1628,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1657,7 +1654,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1683,7 +1680,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1699,9 +1696,7 @@
       <c r="E24" t="s">
         <v>161</v>
       </c>
-      <c r="F24" t="s">
-        <v>239</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24">
         <v>1</v>
       </c>
@@ -1710,7 +1705,7 @@
       </c>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1736,7 +1731,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1762,7 +1757,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -1788,7 +1783,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1814,7 +1809,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1840,7 +1835,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1866,7 +1861,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -1892,7 +1887,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -1918,7 +1913,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -1944,7 +1939,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1967,7 +1962,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -1993,7 +1988,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -2019,7 +2014,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2033,7 +2028,7 @@
         <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F37" t="s">
         <v>179</v>
@@ -2045,7 +2040,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2071,7 +2066,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2085,7 +2080,7 @@
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F39" t="s">
         <v>179</v>
@@ -2097,7 +2092,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2123,7 +2118,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2137,7 +2132,7 @@
         <v>77</v>
       </c>
       <c r="E41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F41" t="s">
         <v>179</v>
@@ -2149,7 +2144,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2175,7 +2170,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2189,7 +2184,7 @@
         <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F43" t="s">
         <v>179</v>
@@ -2201,7 +2196,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2227,7 +2222,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -2241,7 +2236,7 @@
         <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
@@ -2253,7 +2248,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2279,7 +2274,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -2293,7 +2288,7 @@
         <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F47" t="s">
         <v>179</v>
@@ -2305,7 +2300,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>90</v>
       </c>
@@ -2319,7 +2314,7 @@
         <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F48" t="s">
         <v>176</v>
@@ -2331,7 +2326,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>92</v>
       </c>
@@ -2357,7 +2352,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -2383,7 +2378,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -2403,7 +2398,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -2420,7 +2415,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -2437,7 +2432,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>102</v>
       </c>
@@ -2454,7 +2449,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2474,7 +2469,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>106</v>
       </c>
@@ -2491,7 +2486,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -2511,7 +2506,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2528,7 +2523,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -2548,7 +2543,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -2565,7 +2560,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>116</v>
       </c>
@@ -2585,7 +2580,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2602,7 +2597,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2622,7 +2617,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2639,7 +2634,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -2659,7 +2654,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2676,7 +2671,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -2696,7 +2691,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -2713,7 +2708,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -2733,7 +2728,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>134</v>
       </c>
@@ -2750,7 +2745,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>136</v>
       </c>
@@ -2767,7 +2762,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>138</v>
       </c>
@@ -2784,7 +2779,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -2804,7 +2799,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -2821,7 +2816,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -2841,7 +2836,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -2858,7 +2853,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -2875,7 +2870,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>150</v>
       </c>
@@ -2892,7 +2887,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>152</v>
       </c>
@@ -2909,7 +2904,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -2926,7 +2921,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -2947,7 +2942,7 @@
   <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="continuous"/>
+        <filter val="categorical"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC2ADD5-6D0A-40DC-B21A-CFDC2751D9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A196BFB-9593-461C-BA5D-DCFB8898D7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="241">
   <si>
     <t>country_name</t>
   </si>
@@ -581,9 +581,6 @@
     <t>#efedf5,#bcbddc,#756bb1,#54278f</t>
   </si>
   <si>
-    <t>viewable</t>
-  </si>
-  <si>
     <t>scope</t>
   </si>
   <si>
@@ -759,13 +756,19 @@
   </si>
   <si>
     <t>percentage</t>
+  </si>
+  <si>
+    <t>viewable_map</t>
+  </si>
+  <si>
+    <t>viewable_graph</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -782,6 +785,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,13 +822,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,24 +1111,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L81"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="38.88671875" customWidth="1"/>
-    <col min="4" max="4" width="85.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="85.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>168</v>
@@ -1128,19 +1141,22 @@
       <c r="F1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
         <v>169</v>
@@ -1151,19 +1167,22 @@
       <c r="E2" t="s">
         <v>161</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
         <v>169</v>
@@ -1172,21 +1191,24 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
         <v>169</v>
@@ -1200,16 +1222,19 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
         <v>169</v>
@@ -1223,16 +1248,19 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
         <v>169</v>
@@ -1246,16 +1274,19 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
         <v>169</v>
@@ -1264,24 +1295,27 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
@@ -1295,16 +1329,19 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
         <v>169</v>
@@ -1313,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
         <v>175</v>
@@ -1321,16 +1358,19 @@
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
         <v>169</v>
@@ -1342,21 +1382,24 @@
         <v>163</v>
       </c>
       <c r="F10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C11" t="s">
         <v>169</v>
@@ -1368,21 +1411,24 @@
         <v>163</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
         <v>169</v>
@@ -1396,16 +1442,19 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
         <v>169</v>
@@ -1422,16 +1471,19 @@
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
         <v>169</v>
@@ -1443,21 +1495,24 @@
         <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
         <v>169</v>
@@ -1471,16 +1526,19 @@
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
         <v>169</v>
@@ -1489,24 +1547,27 @@
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="H16" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
         <v>169</v>
@@ -1520,16 +1581,19 @@
       <c r="G17">
         <v>0</v>
       </c>
-      <c r="H17" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
         <v>169</v>
@@ -1541,21 +1605,24 @@
         <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
         <v>169</v>
@@ -1564,24 +1631,27 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F19" t="s">
         <v>175</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
         <v>169</v>
@@ -1590,7 +1660,7 @@
         <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F20" t="s">
         <v>175</v>
@@ -1598,16 +1668,19 @@
       <c r="G20">
         <v>1</v>
       </c>
-      <c r="H20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
         <v>169</v>
@@ -1619,21 +1692,24 @@
         <v>163</v>
       </c>
       <c r="F21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="H21" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
         <v>169</v>
@@ -1645,21 +1721,24 @@
         <v>163</v>
       </c>
       <c r="F22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
-      <c r="H22" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
         <v>169</v>
@@ -1668,7 +1747,7 @@
         <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F23" t="s">
         <v>175</v>
@@ -1676,16 +1755,19 @@
       <c r="G23">
         <v>1</v>
       </c>
-      <c r="H23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
         <v>169</v>
@@ -1700,17 +1782,20 @@
       <c r="G24">
         <v>1</v>
       </c>
-      <c r="H24" t="s">
-        <v>184</v>
-      </c>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>183</v>
+      </c>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C25" t="s">
         <v>169</v>
@@ -1722,21 +1807,24 @@
         <v>163</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C26" t="s">
         <v>169</v>
@@ -1745,24 +1833,27 @@
         <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F26" t="s">
         <v>175</v>
       </c>
       <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s">
         <v>169</v>
@@ -1771,7 +1862,7 @@
         <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F27" t="s">
         <v>175</v>
@@ -1779,16 +1870,19 @@
       <c r="G27">
         <v>1</v>
       </c>
-      <c r="H27" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C28" t="s">
         <v>169</v>
@@ -1805,16 +1899,19 @@
       <c r="G28">
         <v>1</v>
       </c>
-      <c r="H28" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C29" t="s">
         <v>169</v>
@@ -1826,21 +1923,24 @@
         <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
-      <c r="H29" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C30" t="s">
         <v>169</v>
@@ -1849,7 +1949,7 @@
         <v>55</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F30" t="s">
         <v>175</v>
@@ -1857,16 +1957,19 @@
       <c r="G30">
         <v>1</v>
       </c>
-      <c r="H30" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C31" t="s">
         <v>169</v>
@@ -1878,21 +1981,24 @@
         <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
-      <c r="H31" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C32" t="s">
         <v>169</v>
@@ -1904,21 +2010,24 @@
         <v>163</v>
       </c>
       <c r="F32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
-      <c r="H32" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s">
         <v>170</v>
@@ -1930,21 +2039,24 @@
         <v>163</v>
       </c>
       <c r="F33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
-      <c r="H33" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C34" t="s">
         <v>170</v>
@@ -1958,16 +2070,19 @@
       <c r="G34">
         <v>0</v>
       </c>
-      <c r="H34" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C35" t="s">
         <v>170</v>
@@ -1976,7 +2091,7 @@
         <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F35" t="s">
         <v>176</v>
@@ -1984,16 +2099,19 @@
       <c r="G35">
         <v>1</v>
       </c>
-      <c r="H35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C36" t="s">
         <v>170</v>
@@ -2002,7 +2120,7 @@
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F36" t="s">
         <v>176</v>
@@ -2010,16 +2128,19 @@
       <c r="G36">
         <v>1</v>
       </c>
-      <c r="H36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C37" t="s">
         <v>170</v>
@@ -2028,7 +2149,7 @@
         <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F37" t="s">
         <v>179</v>
@@ -2036,16 +2157,19 @@
       <c r="G37">
         <v>1</v>
       </c>
-      <c r="H37" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C38" t="s">
         <v>170</v>
@@ -2054,7 +2178,7 @@
         <v>71</v>
       </c>
       <c r="E38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s">
         <v>176</v>
@@ -2062,16 +2186,19 @@
       <c r="G38">
         <v>1</v>
       </c>
-      <c r="H38" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C39" t="s">
         <v>170</v>
@@ -2080,7 +2207,7 @@
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F39" t="s">
         <v>179</v>
@@ -2088,16 +2215,19 @@
       <c r="G39">
         <v>1</v>
       </c>
-      <c r="H39" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
         <v>170</v>
@@ -2106,7 +2236,7 @@
         <v>75</v>
       </c>
       <c r="E40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F40" t="s">
         <v>176</v>
@@ -2114,16 +2244,19 @@
       <c r="G40">
         <v>1</v>
       </c>
-      <c r="H40" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
         <v>170</v>
@@ -2132,7 +2265,7 @@
         <v>77</v>
       </c>
       <c r="E41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F41" t="s">
         <v>179</v>
@@ -2140,16 +2273,19 @@
       <c r="G41">
         <v>1</v>
       </c>
-      <c r="H41" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
         <v>170</v>
@@ -2158,7 +2294,7 @@
         <v>79</v>
       </c>
       <c r="E42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F42" t="s">
         <v>176</v>
@@ -2166,16 +2302,19 @@
       <c r="G42">
         <v>1</v>
       </c>
-      <c r="H42" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C43" t="s">
         <v>170</v>
@@ -2184,7 +2323,7 @@
         <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F43" t="s">
         <v>179</v>
@@ -2192,16 +2331,19 @@
       <c r="G43">
         <v>1</v>
       </c>
-      <c r="H43" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
         <v>170</v>
@@ -2210,7 +2352,7 @@
         <v>83</v>
       </c>
       <c r="E44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F44" t="s">
         <v>176</v>
@@ -2218,16 +2360,19 @@
       <c r="G44">
         <v>1</v>
       </c>
-      <c r="H44" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C45" t="s">
         <v>170</v>
@@ -2236,7 +2381,7 @@
         <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F45" t="s">
         <v>179</v>
@@ -2244,16 +2389,19 @@
       <c r="G45">
         <v>1</v>
       </c>
-      <c r="H45" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
         <v>170</v>
@@ -2262,7 +2410,7 @@
         <v>87</v>
       </c>
       <c r="E46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F46" t="s">
         <v>176</v>
@@ -2270,16 +2418,19 @@
       <c r="G46">
         <v>1</v>
       </c>
-      <c r="H46" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C47" t="s">
         <v>170</v>
@@ -2288,7 +2439,7 @@
         <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F47" t="s">
         <v>179</v>
@@ -2296,16 +2447,19 @@
       <c r="G47">
         <v>1</v>
       </c>
-      <c r="H47" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
         <v>170</v>
@@ -2314,7 +2468,7 @@
         <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F48" t="s">
         <v>176</v>
@@ -2322,16 +2476,19 @@
       <c r="G48">
         <v>1</v>
       </c>
-      <c r="H48" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
         <v>170</v>
@@ -2340,7 +2497,7 @@
         <v>93</v>
       </c>
       <c r="E49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F49" t="s">
         <v>176</v>
@@ -2348,16 +2505,19 @@
       <c r="G49">
         <v>1</v>
       </c>
-      <c r="H49" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>94</v>
       </c>
       <c r="B50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
         <v>170</v>
@@ -2366,7 +2526,7 @@
         <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F50" t="s">
         <v>176</v>
@@ -2374,11 +2534,14 @@
       <c r="G50">
         <v>1</v>
       </c>
-      <c r="H50" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -2394,11 +2557,14 @@
       <c r="G51">
         <v>0</v>
       </c>
-      <c r="H51" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -2411,11 +2577,14 @@
       <c r="G52">
         <v>0</v>
       </c>
-      <c r="H52" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -2428,11 +2597,14 @@
       <c r="G53">
         <v>0</v>
       </c>
-      <c r="H53" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>102</v>
       </c>
@@ -2445,11 +2617,14 @@
       <c r="G54">
         <v>0</v>
       </c>
-      <c r="H54" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2465,11 +2640,14 @@
       <c r="G55">
         <v>0</v>
       </c>
-      <c r="H55" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>106</v>
       </c>
@@ -2482,11 +2660,14 @@
       <c r="G56">
         <v>0</v>
       </c>
-      <c r="H56" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -2502,11 +2683,14 @@
       <c r="G57">
         <v>0</v>
       </c>
-      <c r="H57" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2519,11 +2703,14 @@
       <c r="G58">
         <v>0</v>
       </c>
-      <c r="H58" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -2539,11 +2726,14 @@
       <c r="G59">
         <v>0</v>
       </c>
-      <c r="H59" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -2556,11 +2746,14 @@
       <c r="G60">
         <v>0</v>
       </c>
-      <c r="H60" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>116</v>
       </c>
@@ -2576,11 +2769,14 @@
       <c r="G61">
         <v>0</v>
       </c>
-      <c r="H61" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2593,11 +2789,14 @@
       <c r="G62">
         <v>0</v>
       </c>
-      <c r="H62" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2613,11 +2812,14 @@
       <c r="G63">
         <v>0</v>
       </c>
-      <c r="H63" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2630,11 +2832,14 @@
       <c r="G64">
         <v>0</v>
       </c>
-      <c r="H64" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -2650,11 +2855,14 @@
       <c r="G65">
         <v>0</v>
       </c>
-      <c r="H65" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2667,11 +2875,14 @@
       <c r="G66">
         <v>0</v>
       </c>
-      <c r="H66" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -2687,11 +2898,14 @@
       <c r="G67">
         <v>0</v>
       </c>
-      <c r="H67" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -2704,11 +2918,14 @@
       <c r="G68">
         <v>0</v>
       </c>
-      <c r="H68" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -2724,11 +2941,14 @@
       <c r="G69">
         <v>0</v>
       </c>
-      <c r="H69" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>134</v>
       </c>
@@ -2741,11 +2961,14 @@
       <c r="G70">
         <v>0</v>
       </c>
-      <c r="H70" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>136</v>
       </c>
@@ -2758,11 +2981,14 @@
       <c r="G71">
         <v>0</v>
       </c>
-      <c r="H71" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>138</v>
       </c>
@@ -2775,11 +3001,14 @@
       <c r="G72">
         <v>0</v>
       </c>
-      <c r="H72" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -2795,11 +3024,14 @@
       <c r="G73">
         <v>0</v>
       </c>
-      <c r="H73" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -2812,11 +3044,14 @@
       <c r="G74">
         <v>0</v>
       </c>
-      <c r="H74" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -2832,11 +3067,14 @@
       <c r="G75">
         <v>0</v>
       </c>
-      <c r="H75" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -2849,11 +3087,14 @@
       <c r="G76">
         <v>0</v>
       </c>
-      <c r="H76" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -2866,11 +3107,14 @@
       <c r="G77">
         <v>0</v>
       </c>
-      <c r="H77" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>150</v>
       </c>
@@ -2883,11 +3127,14 @@
       <c r="G78">
         <v>0</v>
       </c>
-      <c r="H78" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>152</v>
       </c>
@@ -2900,11 +3147,14 @@
       <c r="G79">
         <v>0</v>
       </c>
-      <c r="H79" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -2917,11 +3167,14 @@
       <c r="G80">
         <v>0</v>
       </c>
-      <c r="H80" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -2934,18 +3187,15 @@
       <c r="G81">
         <v>0</v>
       </c>
-      <c r="H81" t="s">
-        <v>184</v>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H81" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="categorical"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A196BFB-9593-461C-BA5D-DCFB8898D7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB76754D-849A-4A3B-AD4F-5FE1DE92E401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="234">
   <si>
     <t>country_name</t>
   </si>
@@ -47,138 +47,72 @@
     <t>year</t>
   </si>
   <si>
-    <t>Year of the data entry</t>
-  </si>
-  <si>
     <t>state_name</t>
   </si>
   <si>
     <t>region_name</t>
   </si>
   <si>
-    <t>Name of the country region</t>
-  </si>
-  <si>
     <t>head_name_national</t>
   </si>
   <si>
-    <t>Name of the national head of state (President)</t>
-  </si>
-  <si>
     <t>sex_head_national</t>
   </si>
   <si>
-    <t>Sex of the national head of state (0 = Male, 1 = Female)</t>
-  </si>
-  <si>
     <t>term_head_national</t>
   </si>
   <si>
-    <t>Start and end date of the national government term</t>
-  </si>
-  <si>
     <t>years_nat_gov</t>
   </si>
   <si>
-    <t>Years in office of the national head of state</t>
-  </si>
-  <si>
     <t>reelec_nat_gov</t>
   </si>
   <si>
-    <t>Whether the national head of state was reelected (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>early_exit_nat</t>
   </si>
   <si>
-    <t>Whether the national head of state left office early (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>head_party_national</t>
   </si>
   <si>
-    <t>Political party of the national head of state</t>
-  </si>
-  <si>
     <t>ideo_party_national</t>
   </si>
   <si>
-    <t>Ideology of the national head of state’s party (1-4: Left to Right)</t>
-  </si>
-  <si>
     <t>electoral_national_year</t>
   </si>
   <si>
-    <t>Whether national elections occurred in the year (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>head_name_sub</t>
   </si>
   <si>
-    <t>Name of the subnational head of government (Governor)</t>
-  </si>
-  <si>
     <t>sex_head_sub</t>
   </si>
   <si>
-    <t>Sex of the subnational head of government (0 = Male, 1 = Female)</t>
-  </si>
-  <si>
     <t>term_head_sub</t>
   </si>
   <si>
-    <t>Start and end date of the subnational government term</t>
-  </si>
-  <si>
     <t>change_head_sub</t>
   </si>
   <si>
-    <t>Whether the subnational head of government changed (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>cumulative_changes_head_sub</t>
   </si>
   <si>
-    <t>Total number of changes in the subnational head of government since coding began</t>
-  </si>
-  <si>
     <t>years_sub_gov</t>
   </si>
   <si>
-    <t>Years in office of the subnational head of government</t>
-  </si>
-  <si>
     <t>early_exit_sub</t>
   </si>
   <si>
-    <t>Whether the subnational head of government left office early (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>reelec_sub_gov</t>
   </si>
   <si>
-    <t>Whether the subnational head of government was reelected (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>years_sub_gov_contin</t>
   </si>
   <si>
-    <t>Continuous years the subnational head of government has held office</t>
-  </si>
-  <si>
     <t>head_party_sub</t>
   </si>
   <si>
-    <t>Political party of the subnational head of government</t>
-  </si>
-  <si>
     <t>change_sub_gov_party</t>
   </si>
   <si>
-    <t>Whether the party of the subnational head of government changed (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>cumulative_changes_party_sub</t>
   </si>
   <si>
@@ -188,21 +122,12 @@
     <t>years_sub_gov_party_contin</t>
   </si>
   <si>
-    <t>Continuous years the party of the subnational head of government has held office</t>
-  </si>
-  <si>
     <t>ideo_party_sub</t>
   </si>
   <si>
-    <t>Ideology of the subnational head of government’s party (1-4: Left to Right)</t>
-  </si>
-  <si>
     <t>electoral_sub_year</t>
   </si>
   <si>
-    <t>Whether subnational executive elections occurred in the year (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>cumulative_electoral_sub_year</t>
   </si>
   <si>
@@ -212,45 +137,24 @@
     <t>concurrent_sub_nat_election</t>
   </si>
   <si>
-    <t>Whether subnational and national elections occurred concurrently (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>alignment</t>
   </si>
   <si>
-    <t>Whether the national and subnational heads of government are aligned (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>extraordinary_election</t>
   </si>
   <si>
-    <t>Whether an extraordinary subnational executive election occurred (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>date_electoral_sub</t>
   </si>
   <si>
-    <t>Date of the subnational executive election</t>
-  </si>
-  <si>
     <t>voters_registered_sub</t>
   </si>
   <si>
-    <t>Total registered voters for subnational executive elections</t>
-  </si>
-  <si>
     <t>total_voters_sub</t>
   </si>
   <si>
-    <t>Total votes cast in subnational executive elections</t>
-  </si>
-  <si>
     <t>voter_ratio_sub</t>
   </si>
   <si>
-    <t>Proportion of registered voters who voted (total_voters_sub / voters_registered_sub)</t>
-  </si>
-  <si>
     <t>valid_votes_sub</t>
   </si>
   <si>
@@ -290,15 +194,9 @@
     <t>second_place_votes</t>
   </si>
   <si>
-    <t>Votes received by the second-place candidate</t>
-  </si>
-  <si>
     <t>second_place_ratio</t>
   </si>
   <si>
-    <t>Percentage of votes received by the second-place candidate</t>
-  </si>
-  <si>
     <t>last_place_votes</t>
   </si>
   <si>
@@ -314,9 +212,6 @@
     <t>margin_victory_exe</t>
   </si>
   <si>
-    <t>Difference in vote share between the winner and second-place candidate (v1 - v2)</t>
-  </si>
-  <si>
     <t>num_parties_executive_election_contest</t>
   </si>
   <si>
@@ -539,12 +434,6 @@
     <t>ordinal</t>
   </si>
   <si>
-    <t>Name of the country</t>
-  </si>
-  <si>
-    <t>Name of the subnational unit</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -614,144 +503,15 @@
     <t>Region</t>
   </si>
   <si>
-    <t>Nat. Leader</t>
-  </si>
-  <si>
-    <t>Nat. Leader Sex</t>
-  </si>
-  <si>
-    <t>Nat. Term</t>
-  </si>
-  <si>
-    <t>Nat. Yrs in Office</t>
-  </si>
-  <si>
-    <t>Nat. Reelected</t>
-  </si>
-  <si>
-    <t>Nat. Early Exit</t>
-  </si>
-  <si>
-    <t>Nat. Party</t>
-  </si>
-  <si>
-    <t>Nat. Ideology</t>
-  </si>
-  <si>
-    <t>Nat. Election Yr</t>
-  </si>
-  <si>
-    <t>Subnat. Leader</t>
-  </si>
-  <si>
-    <t>Subnat. Leader Sex</t>
-  </si>
-  <si>
-    <t>Subnat. Term</t>
-  </si>
-  <si>
-    <t>Subnat. Leader Change</t>
-  </si>
-  <si>
-    <t>Subnat. Leader Changes</t>
-  </si>
-  <si>
-    <t>Subnat. Yrs in Office</t>
-  </si>
-  <si>
-    <t>Subnat. Early Exit</t>
-  </si>
-  <si>
-    <t>Subnat. Reelected</t>
-  </si>
-  <si>
-    <t>Subnat. Continuous Yrs</t>
-  </si>
-  <si>
-    <t>Subnat. Party</t>
-  </si>
-  <si>
-    <t>Subnat. Party Change</t>
-  </si>
-  <si>
     <t>Subnat. Party Changes</t>
   </si>
   <si>
-    <t>Subnat. Party Tenure</t>
-  </si>
-  <si>
-    <t>Subnat. Ideology</t>
-  </si>
-  <si>
-    <t>Subnat. Election Yr</t>
-  </si>
-  <si>
     <t>Subnat. Election Count</t>
   </si>
   <si>
-    <t>Concurrent Elections</t>
-  </si>
-  <si>
-    <t>Gov. Alignment</t>
-  </si>
-  <si>
-    <t>Extraordinary Election</t>
-  </si>
-  <si>
-    <t>Subnat. Election Date</t>
-  </si>
-  <si>
-    <t>Reg. Voters</t>
-  </si>
-  <si>
-    <t>Total Votes</t>
-  </si>
-  <si>
-    <t>Turnout Rate</t>
-  </si>
-  <si>
-    <t>Valid Votes</t>
-  </si>
-  <si>
-    <t>Invalid Votes</t>
-  </si>
-  <si>
-    <t>Winner Votes</t>
-  </si>
-  <si>
-    <t>2nd Place Votes</t>
-  </si>
-  <si>
-    <t>Last Place Votes</t>
-  </si>
-  <si>
-    <t>Victory Margin</t>
-  </si>
-  <si>
-    <t>Parties Running</t>
-  </si>
-  <si>
-    <t>Effective Parties</t>
-  </si>
-  <si>
     <t>pretty_name</t>
   </si>
   <si>
-    <t>Valid Vote Ratio</t>
-  </si>
-  <si>
-    <t>Invalid Vote Ratio</t>
-  </si>
-  <si>
-    <t>Winner Ratio</t>
-  </si>
-  <si>
-    <t>2nd Place Ratio</t>
-  </si>
-  <si>
-    <t>Last Place Ratio</t>
-  </si>
-  <si>
     <t>#ff8000,#00E5FF</t>
   </si>
   <si>
@@ -762,6 +522,225 @@
   </si>
   <si>
     <t>viewable_graph</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Name</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natl. Term Length </t>
+  </si>
+  <si>
+    <t>Natl. Yrs in Office</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Reelected</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Early Exit</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Party Name</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Party Ideology</t>
+  </si>
+  <si>
+    <t>Natl. Elections (Head of State)</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Name</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Sex</t>
+  </si>
+  <si>
+    <t>Subnatl. Term Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subnatl. Head of State Alternation </t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Cummulative Alternation</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Years in Office</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Early Exit</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Reelected</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Cummulative Years in Office</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Party Affiliation</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Party Alternation</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Party Cummulative Years in Office</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Party Ideology</t>
+  </si>
+  <si>
+    <t>Subnatl. Elections (Head of State)</t>
+  </si>
+  <si>
+    <t>Natl. Subnatl. Concurrent Elections</t>
+  </si>
+  <si>
+    <t>Natl. Subnatl. Party Alignment</t>
+  </si>
+  <si>
+    <t>Subnatl. Snap Election</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Election Day</t>
+  </si>
+  <si>
+    <t>Subnatl. Registered Voters Total</t>
+  </si>
+  <si>
+    <t>Subnatl. Total Votes</t>
+  </si>
+  <si>
+    <t>Subnatl. Turnout Rate</t>
+  </si>
+  <si>
+    <t>Subnatl. Valid Votes (Executive Elections)</t>
+  </si>
+  <si>
+    <t>Subnatl. Valid Vote Ratio</t>
+  </si>
+  <si>
+    <t>Subnatl. Invalid Votes (Executive Elections)</t>
+  </si>
+  <si>
+    <t>Subnatl. Invalid Vote Ratio</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Votes Received</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Victory Ratio</t>
+  </si>
+  <si>
+    <t>Subnatl. Runner Up Votes Received (Executive Election)</t>
+  </si>
+  <si>
+    <t>Subnatl. Runner Up Vote Ratio (Executive Election)</t>
+  </si>
+  <si>
+    <t>Subnatl. Last Place Votes Received (Executive Elections)</t>
+  </si>
+  <si>
+    <t>Subnatl. Last Place Ratio (Executive Elections)</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Margin of Victory (Executive Elections)</t>
+  </si>
+  <si>
+    <t>Subnatl. Number of Running Parties (Executive Elections)</t>
+  </si>
+  <si>
+    <t>Subnatl. ENP</t>
+  </si>
+  <si>
+    <t>Country Name</t>
+  </si>
+  <si>
+    <t>Year Year</t>
+  </si>
+  <si>
+    <t>State Name</t>
+  </si>
+  <si>
+    <t>Region Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natl. Head of State Name </t>
+  </si>
+  <si>
+    <t>Natl. Head of State Sex (0 = Male, 1 = Female)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natl. Head of State Term Start/End Date </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natl. Head of State </t>
+  </si>
+  <si>
+    <t>Natl. Head of State Reelected (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Early Exit (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Head of State Party Name</t>
+  </si>
+  <si>
+    <t>Natl. Head of State Party Ideology (1-4: Left to Right)</t>
+  </si>
+  <si>
+    <t>Natl. Elections (Head of State) (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Sex (0 = Male, 1 = Female)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subnatl. Head of State Term Start/End Date </t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Alternation (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Early Exit (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Reelected (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Subnatl. Head of State Party Alternation (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Subnatl. Elections (Head of State) (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Natl. Subnatl. Concurrent Elections (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Natl. Subnatl. Party Alignment (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Subnatl. Snap Election (1 = Yes, 0 = No)</t>
+  </si>
+  <si>
+    <t>Date of Subnatl. Election</t>
+  </si>
+  <si>
+    <t>Total Number of Registered Voters (Subnatl. Executive Elections)</t>
+  </si>
+  <si>
+    <t>Total Votes Cast (Subnatl. Executive Elections)</t>
+  </si>
+  <si>
+    <t>Proportion of Registered Voters Who Voted (total_voters_sub / voters_registered_sub)</t>
+  </si>
+  <si>
+    <t>Votes received by the runner up</t>
+  </si>
+  <si>
+    <t>Percentage of votes received by the runner up</t>
+  </si>
+  <si>
+    <t>Difference in vote share between the winner and runner up candidate (v1 - v2)</t>
   </si>
 </sst>
 </file>
@@ -822,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -830,7 +809,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,6 +824,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1124,31 +1106,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1156,25 +1138,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G2" s="5">
+        <v>126</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1182,16 +1164,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1200,24 +1182,24 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1226,24 +1208,24 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1252,24 +1234,24 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1278,27 +1260,27 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="F7" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1307,24 +1289,24 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>210</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1333,27 +1315,27 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F9" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1362,27 +1344,27 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>212</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F10" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1391,27 +1373,27 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1420,24 +1402,24 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1446,27 +1428,27 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1475,27 +1457,27 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
       <c r="E14" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F14" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1504,24 +1486,24 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1530,27 +1512,27 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="F16" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1559,24 +1541,24 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1585,27 +1567,27 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>219</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F18" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1614,27 +1596,27 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="E19" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F19" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1643,27 +1625,27 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1672,27 +1654,27 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F21" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1701,27 +1683,27 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="C22" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1730,27 +1712,27 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F23" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1759,24 +1741,24 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24">
@@ -1786,28 +1768,28 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>222</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1816,27 +1798,27 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F26" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1845,27 +1827,27 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="C27" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F27" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1874,27 +1856,27 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1903,27 +1885,27 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1932,27 +1914,27 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1961,27 +1943,27 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>224</v>
       </c>
       <c r="E31" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F31" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1990,27 +1972,27 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="E32" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2019,27 +2001,27 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="E33" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2048,24 +2030,24 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="C34" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2074,27 +2056,27 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>228</v>
       </c>
       <c r="E35" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F35" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2103,27 +2085,27 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>229</v>
       </c>
       <c r="E36" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F36" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2132,27 +2114,27 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="C37" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>230</v>
       </c>
       <c r="E37" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F37" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2161,27 +2143,27 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F38" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2190,27 +2172,27 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F39" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2219,27 +2201,27 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2248,27 +2230,27 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F41" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2277,27 +2259,27 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F42" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2306,27 +2288,27 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F43" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2335,27 +2317,27 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="E44" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F44" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2364,27 +2346,27 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>232</v>
       </c>
       <c r="E45" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F45" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2393,27 +2375,27 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F46" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2422,27 +2404,27 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="E47" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F47" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2451,27 +2433,27 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>233</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="F48" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2480,27 +2462,27 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="C49" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D49" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F49" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2509,27 +2491,27 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="F50" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2538,21 +2520,21 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2561,18 +2543,18 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2581,18 +2563,18 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2601,18 +2583,18 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2621,21 +2603,21 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F55" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2644,18 +2626,18 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2664,21 +2646,21 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="F57" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2687,18 +2669,18 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D58" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2707,21 +2689,21 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2730,18 +2712,18 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D60" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2750,21 +2732,21 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="F61" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2773,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D62" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2793,21 +2775,21 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="F63" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -2816,18 +2798,18 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D64" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -2836,21 +2818,21 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="F65" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -2859,18 +2841,18 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D66" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -2879,21 +2861,21 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="F67" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2902,18 +2884,18 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -2922,21 +2904,21 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="C69" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F69" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -2945,18 +2927,18 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -2965,18 +2947,18 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2985,18 +2967,18 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="C72" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D72" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3005,21 +2987,21 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D73" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="F73" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3028,18 +3010,18 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -3048,21 +3030,21 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F75" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3071,18 +3053,18 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D76" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3091,18 +3073,18 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3111,18 +3093,18 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C78" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -3131,18 +3113,18 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D79" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3151,18 +3133,18 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="C80" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -3171,18 +3153,18 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D81" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -3191,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB76754D-849A-4A3B-AD4F-5FE1DE92E401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366F64A8-C988-43A0-8603-A822CF2BFFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,10 +824,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1093,6 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1133,7 +1130,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1156,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1185,7 +1182,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1211,7 +1208,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1237,7 +1234,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1263,7 +1260,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1292,7 +1289,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1318,47 +1315,47 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
         <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
         <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -1376,27 +1373,24 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" t="s">
         <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1405,24 +1399,27 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C12" t="s">
         <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>130</v>
+      </c>
+      <c r="F12" t="s">
+        <v>140</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1431,24 +1428,24 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
         <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F13" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1460,53 +1457,53 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
         <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F14" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" t="s">
         <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>148</v>
+      </c>
+      <c r="F15" t="s">
+        <v>157</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1515,27 +1512,24 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
         <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1544,21 +1538,24 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" t="s">
         <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E17" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+      <c r="F17" t="s">
+        <v>157</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1570,18 +1567,18 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
         <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
         <v>128</v>
@@ -1590,7 +1587,7 @@
         <v>157</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1599,85 +1596,83 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
         <v>132</v>
       </c>
       <c r="D19" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
         <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20" t="s">
-        <v>138</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
         <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E21" t="s">
         <v>128</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="3" t="s">
         <v>157</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1686,24 +1681,24 @@
         <v>146</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
         <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1715,52 +1710,54 @@
         <v>146</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
         <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F23" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s">
         <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>157</v>
+      </c>
       <c r="G24">
         <v>1</v>
       </c>
@@ -1772,27 +1769,27 @@
       </c>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C25" t="s">
         <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E25" t="s">
         <v>128</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" t="s">
         <v>157</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1801,85 +1798,76 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="E27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
-        <v>215</v>
-      </c>
-      <c r="E28" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1888,27 +1876,18 @@
         <v>146</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>183</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>223</v>
-      </c>
-      <c r="E29" t="s">
-        <v>128</v>
-      </c>
-      <c r="F29" t="s">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1917,56 +1896,38 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" t="s">
-        <v>147</v>
-      </c>
-      <c r="F30" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>224</v>
-      </c>
-      <c r="E31" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1975,27 +1936,21 @@
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E32" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2004,27 +1959,18 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>226</v>
-      </c>
-      <c r="E33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F33" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2033,21 +1979,18 @@
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>227</v>
-      </c>
-      <c r="E34" t="s">
-        <v>129</v>
+        <v>74</v>
+      </c>
+      <c r="F34" t="s">
+        <v>142</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2059,482 +2002,356 @@
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>188</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" t="s">
-        <v>147</v>
-      </c>
-      <c r="F35" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E36" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>230</v>
-      </c>
-      <c r="E37" t="s">
-        <v>158</v>
-      </c>
-      <c r="F37" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" t="s">
         <v>142</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F38" t="s">
-        <v>139</v>
-      </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" t="s">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" t="s">
-        <v>158</v>
-      </c>
-      <c r="F39" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" t="s">
         <v>142</v>
       </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" t="s">
-        <v>193</v>
-      </c>
-      <c r="C40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" t="s">
-        <v>43</v>
-      </c>
-      <c r="E40" t="s">
-        <v>147</v>
-      </c>
-      <c r="F40" t="s">
-        <v>139</v>
-      </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" t="s">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" t="s">
         <v>142</v>
       </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" t="s">
-        <v>195</v>
-      </c>
-      <c r="C42" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" t="s">
-        <v>147</v>
-      </c>
-      <c r="F42" t="s">
-        <v>139</v>
-      </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" t="s">
-        <v>196</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" t="s">
-        <v>158</v>
-      </c>
-      <c r="F43" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" t="s">
+        <v>96</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F46" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" t="s">
+        <v>102</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" t="s">
+        <v>104</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" t="s">
         <v>142</v>
       </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" t="s">
-        <v>197</v>
-      </c>
-      <c r="C44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" t="s">
-        <v>231</v>
-      </c>
-      <c r="E44" t="s">
-        <v>147</v>
-      </c>
-      <c r="F44" t="s">
-        <v>139</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C45" t="s">
-        <v>133</v>
-      </c>
-      <c r="D45" t="s">
-        <v>232</v>
-      </c>
-      <c r="E45" t="s">
-        <v>158</v>
-      </c>
-      <c r="F45" t="s">
-        <v>142</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" t="s">
-        <v>199</v>
-      </c>
-      <c r="C46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" t="s">
-        <v>147</v>
-      </c>
-      <c r="F46" t="s">
-        <v>139</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" t="s">
-        <v>200</v>
-      </c>
-      <c r="C47" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" t="s">
-        <v>158</v>
-      </c>
-      <c r="F47" t="s">
-        <v>142</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" t="s">
-        <v>201</v>
-      </c>
-      <c r="C48" t="s">
-        <v>133</v>
-      </c>
-      <c r="D48" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" t="s">
-        <v>158</v>
-      </c>
-      <c r="F48" t="s">
-        <v>139</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C49" t="s">
-        <v>133</v>
-      </c>
-      <c r="D49" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" t="s">
-        <v>147</v>
-      </c>
-      <c r="F49" t="s">
-        <v>139</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" t="s">
-        <v>203</v>
-      </c>
-      <c r="C50" t="s">
-        <v>133</v>
-      </c>
-      <c r="D50" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" t="s">
-        <v>149</v>
-      </c>
-      <c r="F50" t="s">
-        <v>139</v>
-      </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
         <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
-      </c>
-      <c r="F51" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2546,15 +2363,18 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
         <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>110</v>
+      </c>
+      <c r="F52" t="s">
+        <v>142</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2566,15 +2386,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
         <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2586,15 +2406,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
         <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2606,18 +2426,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
-      </c>
-      <c r="F55" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2629,15 +2446,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2649,18 +2466,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
-      </c>
-      <c r="F57" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2672,15 +2486,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2694,36 +2508,51 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>164</v>
       </c>
       <c r="C59" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>211</v>
+      </c>
+      <c r="E59" t="s">
+        <v>147</v>
       </c>
       <c r="F59" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="B60" t="s">
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>174</v>
+      </c>
+      <c r="E60" t="s">
+        <v>147</v>
+      </c>
+      <c r="F60" t="s">
+        <v>138</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2737,19 +2566,25 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>18</v>
+      </c>
+      <c r="B61" t="s">
+        <v>175</v>
       </c>
       <c r="C61" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>82</v>
+        <v>175</v>
+      </c>
+      <c r="E61" t="s">
+        <v>147</v>
       </c>
       <c r="F61" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2760,16 +2595,25 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>21</v>
+      </c>
+      <c r="B62" t="s">
+        <v>178</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>178</v>
+      </c>
+      <c r="E62" t="s">
+        <v>147</v>
+      </c>
+      <c r="F62" t="s">
+        <v>138</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2780,22 +2624,28 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>24</v>
+      </c>
+      <c r="B63" t="s">
+        <v>154</v>
       </c>
       <c r="C63" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>25</v>
+      </c>
+      <c r="E63" t="s">
+        <v>147</v>
       </c>
       <c r="F63" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
         <v>146</v>
@@ -2803,19 +2653,28 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>26</v>
+      </c>
+      <c r="B64" t="s">
+        <v>181</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D64" t="s">
-        <v>88</v>
+        <v>181</v>
+      </c>
+      <c r="E64" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" t="s">
+        <v>138</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="s">
         <v>146</v>
@@ -2823,22 +2682,28 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>29</v>
+      </c>
+      <c r="B65" t="s">
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>30</v>
+      </c>
+      <c r="E65" t="s">
+        <v>147</v>
       </c>
       <c r="F65" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="s">
         <v>146</v>
@@ -2846,19 +2711,28 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>35</v>
+      </c>
+      <c r="B66" t="s">
+        <v>188</v>
       </c>
       <c r="C66" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>228</v>
+      </c>
+      <c r="E66" t="s">
+        <v>147</v>
+      </c>
+      <c r="F66" t="s">
+        <v>139</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="s">
         <v>146</v>
@@ -2866,22 +2740,28 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>36</v>
+      </c>
+      <c r="B67" t="s">
+        <v>189</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D67" t="s">
-        <v>94</v>
+        <v>229</v>
+      </c>
+      <c r="E67" t="s">
+        <v>147</v>
       </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="s">
         <v>146</v>
@@ -2889,19 +2769,28 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>190</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D68" t="s">
-        <v>96</v>
+        <v>230</v>
+      </c>
+      <c r="E68" t="s">
+        <v>158</v>
+      </c>
+      <c r="F68" t="s">
+        <v>142</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="s">
         <v>146</v>
@@ -2909,22 +2798,28 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>38</v>
+      </c>
+      <c r="B69" t="s">
+        <v>191</v>
       </c>
       <c r="C69" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>98</v>
+        <v>39</v>
+      </c>
+      <c r="E69" t="s">
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
         <v>146</v>
@@ -2932,19 +2827,28 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>41</v>
+      </c>
+      <c r="E70" t="s">
+        <v>158</v>
+      </c>
+      <c r="F70" t="s">
+        <v>142</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="s">
         <v>146</v>
@@ -2952,19 +2856,28 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>42</v>
+      </c>
+      <c r="B71" t="s">
+        <v>193</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>102</v>
+        <v>43</v>
+      </c>
+      <c r="E71" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" t="s">
+        <v>139</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="s">
         <v>146</v>
@@ -2972,19 +2885,28 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>45</v>
+      </c>
+      <c r="E72" t="s">
+        <v>158</v>
+      </c>
+      <c r="F72" t="s">
+        <v>142</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="s">
         <v>146</v>
@@ -2992,22 +2914,28 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>46</v>
+      </c>
+      <c r="B73" t="s">
+        <v>195</v>
       </c>
       <c r="C73" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>47</v>
+      </c>
+      <c r="E73" t="s">
+        <v>147</v>
       </c>
       <c r="F73" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="s">
         <v>146</v>
@@ -3015,19 +2943,28 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>48</v>
+      </c>
+      <c r="B74" t="s">
+        <v>196</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D74" t="s">
-        <v>108</v>
+        <v>49</v>
+      </c>
+      <c r="E74" t="s">
+        <v>158</v>
+      </c>
+      <c r="F74" t="s">
+        <v>142</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="s">
         <v>146</v>
@@ -3035,22 +2972,28 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>109</v>
+        <v>50</v>
+      </c>
+      <c r="B75" t="s">
+        <v>197</v>
       </c>
       <c r="C75" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>231</v>
+      </c>
+      <c r="E75" t="s">
+        <v>147</v>
       </c>
       <c r="F75" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="s">
         <v>146</v>
@@ -3058,19 +3001,28 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>111</v>
+        <v>51</v>
+      </c>
+      <c r="B76" t="s">
+        <v>198</v>
       </c>
       <c r="C76" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
-        <v>112</v>
+        <v>232</v>
+      </c>
+      <c r="E76" t="s">
+        <v>158</v>
+      </c>
+      <c r="F76" t="s">
+        <v>142</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="s">
         <v>146</v>
@@ -3078,19 +3030,28 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>113</v>
+        <v>52</v>
+      </c>
+      <c r="B77" t="s">
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>53</v>
+      </c>
+      <c r="E77" t="s">
+        <v>147</v>
+      </c>
+      <c r="F77" t="s">
+        <v>139</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="s">
         <v>146</v>
@@ -3098,19 +3059,28 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>115</v>
+        <v>54</v>
+      </c>
+      <c r="B78" t="s">
+        <v>200</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
-        <v>116</v>
+        <v>55</v>
+      </c>
+      <c r="E78" t="s">
+        <v>158</v>
+      </c>
+      <c r="F78" t="s">
+        <v>142</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="s">
         <v>146</v>
@@ -3118,19 +3088,28 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>117</v>
+        <v>56</v>
+      </c>
+      <c r="B79" t="s">
+        <v>201</v>
       </c>
       <c r="C79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>118</v>
+        <v>233</v>
+      </c>
+      <c r="E79" t="s">
+        <v>158</v>
+      </c>
+      <c r="F79" t="s">
+        <v>139</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="s">
         <v>146</v>
@@ -3138,19 +3117,28 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>119</v>
+        <v>57</v>
+      </c>
+      <c r="B80" t="s">
+        <v>202</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>58</v>
+      </c>
+      <c r="E80" t="s">
+        <v>147</v>
+      </c>
+      <c r="F80" t="s">
+        <v>139</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="s">
         <v>146</v>
@@ -3158,26 +3146,44 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>121</v>
+        <v>59</v>
+      </c>
+      <c r="B81" t="s">
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>122</v>
+        <v>60</v>
+      </c>
+      <c r="E81" t="s">
+        <v>149</v>
+      </c>
+      <c r="F81" t="s">
+        <v>139</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="s">
         <v>146</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I81" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I81">
+      <sortCondition ref="H1:H81"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366F64A8-C988-43A0-8603-A822CF2BFFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE33F7A1-0DCB-4C90-A7D3-A0130066A056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="235">
   <si>
     <t>country_name</t>
   </si>
@@ -741,6 +741,9 @@
   </si>
   <si>
     <t>Difference in vote share between the winner and runner up candidate (v1 - v2)</t>
+  </si>
+  <si>
+    <t>#FF5454,#CDFC00,#14EC00</t>
   </si>
 </sst>
 </file>
@@ -801,7 +804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -809,6 +812,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,7 +1094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -1260,7 +1264,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1277,7 +1281,7 @@
         <v>148</v>
       </c>
       <c r="F7" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1483,7 +1487,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1500,7 +1504,7 @@
         <v>148</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2506,7 +2510,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2535,7 +2539,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2564,7 +2568,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -2593,7 +2597,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2651,7 +2655,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -2680,7 +2684,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>29</v>
       </c>
@@ -2709,7 +2713,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2738,7 +2742,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>36</v>
       </c>
@@ -2767,7 +2771,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>37</v>
       </c>
@@ -2796,7 +2800,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -2825,7 +2829,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -2854,7 +2858,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>42</v>
       </c>
@@ -2883,7 +2887,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>44</v>
       </c>
@@ -2912,7 +2916,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>46</v>
       </c>
@@ -2941,7 +2945,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -2970,7 +2974,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>50</v>
       </c>
@@ -2999,7 +3003,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>51</v>
       </c>
@@ -3028,7 +3032,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>52</v>
       </c>
@@ -3057,7 +3061,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>54</v>
       </c>
@@ -3086,7 +3090,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>56</v>
       </c>
@@ -3115,7 +3119,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>57</v>
       </c>
@@ -3144,7 +3148,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>59</v>
       </c>
@@ -3173,11 +3177,14 @@
         <v>146</v>
       </c>
     </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F82" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I81" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="7">
+    <filterColumn colId="4">
       <filters>
-        <filter val="1"/>
+        <filter val="gender"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I81">
